--- a/CG_2569_บันทึกผลจริง_template.xlsx
+++ b/CG_2569_บันทึกผลจริง_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://meacloud-my.sharepoint.com/personal/2543024_meanet_mea_or_th/Documents/งานการไฟฟ้านครหลวง/งานปี2569/Dashborad/Dashborad_CG/DB_CG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devill/1_กฟน./2569/Dashborad_CG/DB_CG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="305" documentId="11_2F551DB17E9CDF94015972A66DF2E71E32C6BFB9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF4A56E8-1A3B-6349-904F-15D259C8A842}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2B6078-77B0-8C49-A218-51C477A541B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="14720" windowHeight="17060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="คำแนะนำ" sheetId="1" r:id="rId1"/>
@@ -34,56 +34,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 30.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 30.0%</t>
         </r>
       </text>
     </comment>
@@ -92,56 +48,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 60.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 60.0%</t>
         </r>
       </text>
     </comment>
@@ -290,56 +202,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 5.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 5.0%</t>
         </r>
       </text>
     </comment>
@@ -362,56 +230,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 15.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 15.0%</t>
         </r>
       </text>
     </comment>
@@ -420,56 +244,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -520,56 +300,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ส</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 80.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ส.ค.: 80.0%</t>
         </r>
       </text>
     </comment>
@@ -648,56 +384,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -706,56 +398,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 40.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 40.0%</t>
         </r>
       </text>
     </comment>
@@ -778,56 +426,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 80.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 80.0%</t>
         </r>
       </text>
     </comment>
@@ -850,56 +454,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 100.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ค.: 100.0%</t>
         </r>
       </text>
     </comment>
@@ -1006,56 +566,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 0%</t>
         </r>
       </text>
     </comment>
@@ -1064,56 +580,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 0%</t>
         </r>
       </text>
     </comment>
@@ -1454,56 +926,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 40.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 40.0%</t>
         </r>
       </text>
     </comment>
@@ -1512,56 +940,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 50.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 50.0%</t>
         </r>
       </text>
     </comment>
@@ -2074,56 +1458,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มิ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 80.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 80.0%</t>
         </r>
       </text>
     </comment>
@@ -2632,56 +1972,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มิ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 40.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 40.0%</t>
         </r>
       </text>
     </comment>
@@ -2942,56 +2238,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 10.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 10.0%</t>
         </r>
       </text>
     </comment>
@@ -3000,56 +2252,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -3100,56 +2308,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มิ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 60.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 60.0%</t>
         </r>
       </text>
     </comment>
@@ -3448,56 +2612,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 30.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 30.0%</t>
         </r>
       </text>
     </comment>
@@ -3646,56 +2766,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 0%</t>
         </r>
       </text>
     </comment>
@@ -3844,56 +2920,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 30.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 30.0%</t>
         </r>
       </text>
     </comment>
@@ -3902,56 +2934,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 60.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 60.0%</t>
         </r>
       </text>
     </comment>
@@ -3988,56 +2976,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 100.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 100.0%</t>
         </r>
       </text>
     </comment>
@@ -4158,56 +3102,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -4258,56 +3158,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มิ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 60.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 60.0%</t>
         </r>
       </text>
     </comment>
@@ -4316,56 +3172,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 70.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ค.: 70.0%</t>
         </r>
       </text>
     </comment>
@@ -4458,56 +3270,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 0%</t>
         </r>
       </text>
     </comment>
@@ -4516,56 +3284,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 0%</t>
         </r>
       </text>
     </comment>
@@ -4574,56 +3298,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 0%</t>
         </r>
       </text>
     </comment>
@@ -4786,56 +3466,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 40.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 40.0%</t>
         </r>
       </text>
     </comment>
@@ -4844,56 +3480,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 50.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 50.0%</t>
         </r>
       </text>
     </comment>
@@ -4930,56 +3522,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ส</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 80.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ส.ค.: 80.0%</t>
         </r>
       </text>
     </comment>
@@ -5226,56 +3774,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 0%</t>
         </r>
       </text>
     </comment>
@@ -5438,56 +3942,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -5496,56 +3956,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 30.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 30.0%</t>
         </r>
       </text>
     </comment>
@@ -5582,56 +3998,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มิ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 60.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 60.0%</t>
         </r>
       </text>
     </comment>
@@ -5738,56 +4110,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 0%</t>
         </r>
       </text>
     </comment>
@@ -5796,56 +4124,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 0%</t>
         </r>
       </text>
     </comment>
@@ -5868,56 +4152,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 0%</t>
         </r>
       </text>
     </comment>
@@ -5926,56 +4166,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มิ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 10.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 10.0%</t>
         </r>
       </text>
     </comment>
@@ -5984,56 +4180,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ค.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -6308,56 +4460,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 30.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 30.0%</t>
         </r>
       </text>
     </comment>
@@ -6380,56 +4488,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 50.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 50.0%</t>
         </r>
       </text>
     </comment>
@@ -6438,56 +4502,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มิ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 60.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 60.0%</t>
         </r>
       </text>
     </comment>
@@ -6496,56 +4516,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 70.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ค.: 70.0%</t>
         </r>
       </text>
     </comment>
@@ -6694,56 +4670,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มิ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 100.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 100.0%</t>
         </r>
       </text>
     </comment>
@@ -7004,56 +4936,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 0%</t>
         </r>
       </text>
     </comment>
@@ -7062,56 +4950,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 0%</t>
         </r>
       </text>
     </comment>
@@ -7162,56 +5006,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มิ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 0%</t>
         </r>
       </text>
     </comment>
@@ -7304,56 +5104,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 10.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 10.0%</t>
         </r>
       </text>
     </comment>
@@ -7362,56 +5118,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -7560,56 +5272,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 0%</t>
         </r>
       </text>
     </comment>
@@ -7968,56 +5636,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 60.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 60.0%</t>
         </r>
       </text>
     </comment>
@@ -8166,56 +5790,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -8392,56 +5972,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>มี</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 100.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 100.0%</t>
         </r>
       </text>
     </comment>
@@ -8954,56 +6490,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 0%</t>
         </r>
       </text>
     </comment>
@@ -9124,56 +6616,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -9336,56 +6784,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 10.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 10.0%</t>
         </r>
       </text>
     </comment>
@@ -9394,56 +6798,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -9592,56 +6952,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 0%</t>
         </r>
       </text>
     </comment>
@@ -9678,56 +6994,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ย</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 0%</t>
         </r>
       </text>
     </comment>
@@ -9736,56 +7008,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 0%</t>
         </r>
       </text>
     </comment>
@@ -10396,56 +7624,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ม</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 10.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 10.0%</t>
         </r>
       </text>
     </comment>
@@ -10454,56 +7638,12 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ก</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>พ</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 20.0%</t>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 20.0%</t>
         </r>
       </text>
     </comment>
@@ -11660,7 +8800,130 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="170">
+  <si>
+    <t>แผนองค์กรโปร่งใสมีคุณธรรมตามแนวทาง ITA (Integrity and Transparency Assessment) ประจำปี 2569</t>
+  </si>
+  <si>
+    <t>ตัวชี้วัด: ผลการประเมินคุณธรรมและความโปร่งใสในการดำเนินงานของหน่วยงานภาครัฐโดยสำนักงาน ป.ป.ช. ได้ ≥ 90 คะแนน   |   งบประมาณ: 0.28 ล้านบาท   |   ผู้รับผิดชอบหลัก: ฝบส.</t>
+  </si>
+  <si>
+    <t>ลำดับ</t>
+  </si>
+  <si>
+    <t>กิจกรรม</t>
+  </si>
+  <si>
+    <t>หน่วยงาน</t>
+  </si>
+  <si>
+    <t>น้ำหนัก</t>
+  </si>
+  <si>
+    <t>ม.ค.</t>
+  </si>
+  <si>
+    <t>ก.พ.</t>
+  </si>
+  <si>
+    <t>มี.ค.</t>
+  </si>
+  <si>
+    <t>เม.ย.</t>
+  </si>
+  <si>
+    <t>พ.ค.</t>
+  </si>
+  <si>
+    <t>มิ.ย.</t>
+  </si>
+  <si>
+    <t>ก.ค.</t>
+  </si>
+  <si>
+    <t>ส.ค.</t>
+  </si>
+  <si>
+    <t>ก.ย.</t>
+  </si>
+  <si>
+    <t>ต.ค.</t>
+  </si>
+  <si>
+    <t>พ.ย.</t>
+  </si>
+  <si>
+    <t>ธ.ค.</t>
+  </si>
+  <si>
+    <t>ปัญหา/อุปสรรค (ใช้ภายใน)</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ ม.ค.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ ก.พ.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ มี.ค.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ เม.ย.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ พ.ค.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ มิ.ย.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ ก.ค.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ ส.ค.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ ก.ย.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ ต.ค.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ พ.ย.</t>
+  </si>
+  <si>
+    <t>สิ่งที่ดำเนินการ ธ.ค.</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>กำหนดแนวทางการปรับปรุง โดยร่วมรับฟังคำชี้แจงเกณฑ์การประเมิน ITA และแลกเปลี่ยนความรู้กับเครือข่ายรัฐวิสาหกิจ รวมทั้งผลการวิเคราะห์ GAP ปีที่ผ่านมา ผลผลิต แนวทางการปรับปรุงเพื่อพัฒนา การดำเนินงานให้เป็นไปตามเกณฑ์ ITA</t>
+  </si>
+  <si>
+    <t>ฝบส.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>ดำเนินงานตามแนวทางการปรับปรุง ทั้งการเปิดเผยข้อมูลและการสร้างการรับรู้ให้กับผู้มีส่วนได้ส่วนเสีย ผลผลิต มีการเปิดเผยข้อมูลตามแนวทาง ITA และ ผู้มีส่วนได้ส่วนเสียรับรู้การดำเนินงานอย่างโปร่งใสขององค์กร</t>
+  </si>
+  <si>
+    <t>ฝบส. หน่วยงาน ที่เกี่ยวข้อง</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>จัดทำข้อมูลผู้มีส่วนได้ส่วนเสียเข้าระบบสำนักงาน ป.ป.ช. และประชาสัมพันธ์ให้ผู้มีส่วนได้ส่วนเสียดำเนินการประเมิน ITA ผลผลิต ผู้มีส่วนได้ส่วนเสียประเมิน ITA</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>จัดทำและวิเคราะห์รายงานผลการประเมิน ITA ผลผลิต รายงานผลการประเมิน ITA</t>
+  </si>
   <si>
     <t>แบบฟอร์มบันทึกผลการดำเนินงานแผนงาน CG ประจำปี 2569</t>
   </si>
@@ -11689,93 +8952,6 @@
     <t>หมายเหตุสำคัญ: ค่าผลจริงเป็น "ร้อยละความคืบหน้าสะสม" ของกิจกรรมนั้น เทียบกับเป้าหมายสะสมของเดือนเดียวกัน</t>
   </si>
   <si>
-    <t>แผนองค์กรโปร่งใสมีคุณธรรมตามแนวทาง ITA (Integrity and Transparency Assessment) ประจำปี 2569</t>
-  </si>
-  <si>
-    <t>ตัวชี้วัด: ผลการประเมินคุณธรรมและความโปร่งใสในการดำเนินงานของหน่วยงานภาครัฐโดยสำนักงาน ป.ป.ช. ได้ ≥ 90 คะแนน   |   งบประมาณ: 0.28 ล้านบาท   |   ผู้รับผิดชอบหลัก: ฝบส.</t>
-  </si>
-  <si>
-    <t>ลำดับ</t>
-  </si>
-  <si>
-    <t>กิจกรรม</t>
-  </si>
-  <si>
-    <t>หน่วยงาน</t>
-  </si>
-  <si>
-    <t>น้ำหนัก</t>
-  </si>
-  <si>
-    <t>ม.ค.</t>
-  </si>
-  <si>
-    <t>ก.พ.</t>
-  </si>
-  <si>
-    <t>มี.ค.</t>
-  </si>
-  <si>
-    <t>เม.ย.</t>
-  </si>
-  <si>
-    <t>พ.ค.</t>
-  </si>
-  <si>
-    <t>มิ.ย.</t>
-  </si>
-  <si>
-    <t>ก.ค.</t>
-  </si>
-  <si>
-    <t>ส.ค.</t>
-  </si>
-  <si>
-    <t>ก.ย.</t>
-  </si>
-  <si>
-    <t>ต.ค.</t>
-  </si>
-  <si>
-    <t>พ.ย.</t>
-  </si>
-  <si>
-    <t>ธ.ค.</t>
-  </si>
-  <si>
-    <t>ปัญหา/อุปสรรค (ใช้ภายใน)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>กำหนดแนวทางการปรับปรุง โดยร่วมรับฟังคำชี้แจงเกณฑ์การประเมิน ITA และแลกเปลี่ยนความรู้กับเครือข่ายรัฐวิสาหกิจ รวมทั้งผลการวิเคราะห์ GAP ปีที่ผ่านมา ผลผลิต แนวทางการปรับปรุงเพื่อพัฒนา การดำเนินงานให้เป็นไปตามเกณฑ์ ITA</t>
-  </si>
-  <si>
-    <t>ฝบส.</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>ดำเนินงานตามแนวทางการปรับปรุง ทั้งการเปิดเผยข้อมูลและการสร้างการรับรู้ให้กับผู้มีส่วนได้ส่วนเสีย ผลผลิต มีการเปิดเผยข้อมูลตามแนวทาง ITA และ ผู้มีส่วนได้ส่วนเสียรับรู้การดำเนินงานอย่างโปร่งใสขององค์กร</t>
-  </si>
-  <si>
-    <t>ฝบส. หน่วยงาน ที่เกี่ยวข้อง</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>จัดทำข้อมูลผู้มีส่วนได้ส่วนเสียเข้าระบบสำนักงาน ป.ป.ช. และประชาสัมพันธ์ให้ผู้มีส่วนได้ส่วนเสียดำเนินการประเมิน ITA ผลผลิต ผู้มีส่วนได้ส่วนเสียประเมิน ITA</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>จัดทำและวิเคราะห์รายงานผลการประเมิน ITA ผลผลิต รายงานผลการประเมิน ITA</t>
-  </si>
-  <si>
     <t>แผนส่งเสริมองค์กรคุณธรรม ประจำปี 2569</t>
   </si>
   <si>
@@ -12125,13 +9301,22 @@
   </si>
   <si>
     <t>พัฒนา ประเมินคุณภาพ/ประสิทธิผลของกระบวนการติดตามและรายงานผลการดำเนินงานด้านการเงินและไม่ใช่การเงิน ผลผลิต มีกระบวนการที่สามารถนำไปปฏิบัติได้ และมีผลการประเมินกระบวนการเป็นข้อมูลประกอบการปรับปรุง</t>
+  </si>
+  <si>
+    <t>อยู่ระหว่างดำเนินการ</t>
+  </si>
+  <si>
+    <t>ยังไม่ดำเนินการ</t>
+  </si>
+  <si>
+    <t>ดำเนินการเสร็จสิ้น</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12198,12 +9383,6 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -12243,7 +9422,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -12266,11 +9445,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC8D4CE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC8D4CE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC8D4CE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC8D4CE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC8D4CE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -12305,17 +9508,18 @@
     <xf numFmtId="1" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12331,10 +9535,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12629,49 +9829,49 @@
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="21" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -12681,7 +9881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -12690,11 +9890,12 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="16" width="6.5" customWidth="1"/>
     <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="18" max="29" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>9</v>
+    <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -12714,9 +9915,9 @@
       <c r="Q1" s="13"/>
       <c r="R1" s="13"/>
     </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>10</v>
+    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>1</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -12736,68 +9937,104 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="Q4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="R4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="S4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="T4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="U4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="V4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="W4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="X4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Y4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="AA4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="10">
         <v>20</v>
@@ -12821,16 +10058,25 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="8"/>
+      <c r="R5" t="s">
+        <v>167</v>
+      </c>
+      <c r="S5" t="s">
+        <v>167</v>
+      </c>
+      <c r="T5" t="s">
+        <v>169</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6" s="10">
         <v>30</v>
@@ -12860,16 +10106,34 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="8"/>
+      <c r="R6" t="s">
+        <v>167</v>
+      </c>
+      <c r="S6" t="s">
+        <v>167</v>
+      </c>
+      <c r="T6" t="s">
+        <v>167</v>
+      </c>
+      <c r="U6" t="s">
+        <v>167</v>
+      </c>
+      <c r="V6" t="s">
+        <v>167</v>
+      </c>
+      <c r="W6" t="s">
+        <v>167</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D7" s="10">
         <v>25</v>
@@ -12897,16 +10161,34 @@
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="8"/>
+      <c r="R7" t="s">
+        <v>168</v>
+      </c>
+      <c r="S7" t="s">
+        <v>167</v>
+      </c>
+      <c r="T7" t="s">
+        <v>167</v>
+      </c>
+      <c r="U7" t="s">
+        <v>167</v>
+      </c>
+      <c r="V7" t="s">
+        <v>167</v>
+      </c>
+      <c r="W7" t="s">
+        <v>169</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" s="10">
         <v>25</v>
@@ -12932,16 +10214,37 @@
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="8"/>
+      <c r="R8" t="s">
+        <v>168</v>
+      </c>
+      <c r="S8" t="s">
+        <v>168</v>
+      </c>
+      <c r="T8" t="s">
+        <v>168</v>
+      </c>
+      <c r="U8" t="s">
+        <v>168</v>
+      </c>
+      <c r="V8" t="s">
+        <v>168</v>
+      </c>
+      <c r="W8" t="s">
+        <v>168</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="whole" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรอกค่าร้อยละ 0–100" promptTitle="บันทึกผลจริง" prompt="ผลจริงสะสม (%) 0–100" sqref="E5:P8" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>0</formula1>
       <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5:AC8" xr:uid="{F52735A3-F824-6446-A6D9-D92A994180F3}">
+      <formula1>"ยังไม่ดำเนินการ,อยู่ระหว่างดำเนินการ,ดำเนินการเสร็จสิ้น"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12951,7 +10254,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -12960,11 +10263,12 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="16" width="6.5" customWidth="1"/>
     <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="18" max="29" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>38</v>
+    <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -12984,9 +10288,9 @@
       <c r="Q1" s="13"/>
       <c r="R1" s="13"/>
     </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>39</v>
+    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -13006,68 +10310,104 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="Q4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="R4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="S4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="T4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="U4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="V4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="W4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="X4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Y4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="AA4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="10">
         <v>15</v>
@@ -13097,16 +10437,52 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="8"/>
+      <c r="R5" t="s">
+        <v>168</v>
+      </c>
+      <c r="S5" t="s">
+        <v>168</v>
+      </c>
+      <c r="T5" t="s">
+        <v>168</v>
+      </c>
+      <c r="U5" t="s">
+        <v>168</v>
+      </c>
+      <c r="V5" t="s">
+        <v>168</v>
+      </c>
+      <c r="W5" t="s">
+        <v>168</v>
+      </c>
+      <c r="X5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" s="10">
         <v>20</v>
@@ -13136,16 +10512,52 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="8"/>
+      <c r="R6" t="s">
+        <v>168</v>
+      </c>
+      <c r="S6" t="s">
+        <v>168</v>
+      </c>
+      <c r="T6" t="s">
+        <v>168</v>
+      </c>
+      <c r="U6" t="s">
+        <v>168</v>
+      </c>
+      <c r="V6" t="s">
+        <v>168</v>
+      </c>
+      <c r="W6" t="s">
+        <v>168</v>
+      </c>
+      <c r="X6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D7" s="10">
         <v>20</v>
@@ -13175,16 +10587,52 @@
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="8"/>
+      <c r="R7" t="s">
+        <v>168</v>
+      </c>
+      <c r="S7" t="s">
+        <v>168</v>
+      </c>
+      <c r="T7" t="s">
+        <v>168</v>
+      </c>
+      <c r="U7" t="s">
+        <v>168</v>
+      </c>
+      <c r="V7" t="s">
+        <v>168</v>
+      </c>
+      <c r="W7" t="s">
+        <v>168</v>
+      </c>
+      <c r="X7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" s="10">
         <v>10</v>
@@ -13214,16 +10662,52 @@
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="8"/>
+      <c r="R8" t="s">
+        <v>168</v>
+      </c>
+      <c r="S8" t="s">
+        <v>168</v>
+      </c>
+      <c r="T8" t="s">
+        <v>168</v>
+      </c>
+      <c r="U8" t="s">
+        <v>168</v>
+      </c>
+      <c r="V8" t="s">
+        <v>168</v>
+      </c>
+      <c r="W8" t="s">
+        <v>168</v>
+      </c>
+      <c r="X8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="9" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D9" s="10">
         <v>20</v>
@@ -13253,16 +10737,52 @@
       <c r="O9" s="11"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="8"/>
+      <c r="R9" t="s">
+        <v>168</v>
+      </c>
+      <c r="S9" t="s">
+        <v>168</v>
+      </c>
+      <c r="T9" t="s">
+        <v>168</v>
+      </c>
+      <c r="U9" t="s">
+        <v>168</v>
+      </c>
+      <c r="V9" t="s">
+        <v>168</v>
+      </c>
+      <c r="W9" t="s">
+        <v>168</v>
+      </c>
+      <c r="X9" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="10" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D10" s="10">
         <v>15</v>
@@ -13292,16 +10812,55 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="8"/>
+      <c r="R10" t="s">
+        <v>168</v>
+      </c>
+      <c r="S10" t="s">
+        <v>168</v>
+      </c>
+      <c r="T10" t="s">
+        <v>168</v>
+      </c>
+      <c r="U10" t="s">
+        <v>168</v>
+      </c>
+      <c r="V10" t="s">
+        <v>168</v>
+      </c>
+      <c r="W10" t="s">
+        <v>168</v>
+      </c>
+      <c r="X10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>168</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="whole" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรอกค่าร้อยละ 0–100" promptTitle="บันทึกผลจริง" prompt="ผลจริงสะสม (%) 0–100" sqref="E5:P10" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>0</formula1>
       <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5:AC10" xr:uid="{2777AE01-D72E-6A4D-95C6-856F41EC9BD1}">
+      <formula1>"ยังไม่ดำเนินการ,อยู่ระหว่างดำเนินการ,ดำเนินการเสร็จสิ้น"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13311,7 +10870,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -13320,11 +10879,12 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="16" width="6.5" customWidth="1"/>
     <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="18" max="29" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>48</v>
+    <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -13344,9 +10904,9 @@
       <c r="Q1" s="13"/>
       <c r="R1" s="13"/>
     </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>49</v>
+    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -13366,68 +10926,104 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="Q4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="R4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="S4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="T4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="U4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="V4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="W4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="X4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Y4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="AA4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="10">
         <v>20</v>
@@ -13457,16 +11053,52 @@
       <c r="O5" s="11"/>
       <c r="P5" s="11"/>
       <c r="Q5" s="8"/>
+      <c r="R5" t="s">
+        <v>168</v>
+      </c>
+      <c r="S5" t="s">
+        <v>168</v>
+      </c>
+      <c r="T5" t="s">
+        <v>168</v>
+      </c>
+      <c r="U5" t="s">
+        <v>168</v>
+      </c>
+      <c r="V5" t="s">
+        <v>168</v>
+      </c>
+      <c r="W5" t="s">
+        <v>168</v>
+      </c>
+      <c r="X5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D6" s="10">
         <v>20</v>
@@ -13496,16 +11128,52 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="8"/>
+      <c r="R6" t="s">
+        <v>168</v>
+      </c>
+      <c r="S6" t="s">
+        <v>168</v>
+      </c>
+      <c r="T6" t="s">
+        <v>168</v>
+      </c>
+      <c r="U6" t="s">
+        <v>168</v>
+      </c>
+      <c r="V6" t="s">
+        <v>168</v>
+      </c>
+      <c r="W6" t="s">
+        <v>168</v>
+      </c>
+      <c r="X6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D7" s="10">
         <v>30</v>
@@ -13535,16 +11203,52 @@
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="8"/>
+      <c r="R7" t="s">
+        <v>168</v>
+      </c>
+      <c r="S7" t="s">
+        <v>168</v>
+      </c>
+      <c r="T7" t="s">
+        <v>168</v>
+      </c>
+      <c r="U7" t="s">
+        <v>168</v>
+      </c>
+      <c r="V7" t="s">
+        <v>168</v>
+      </c>
+      <c r="W7" t="s">
+        <v>168</v>
+      </c>
+      <c r="X7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" s="10">
         <v>30</v>
@@ -13574,16 +11278,55 @@
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="8"/>
+      <c r="R8" t="s">
+        <v>168</v>
+      </c>
+      <c r="S8" t="s">
+        <v>168</v>
+      </c>
+      <c r="T8" t="s">
+        <v>168</v>
+      </c>
+      <c r="U8" t="s">
+        <v>168</v>
+      </c>
+      <c r="V8" t="s">
+        <v>168</v>
+      </c>
+      <c r="W8" t="s">
+        <v>168</v>
+      </c>
+      <c r="X8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>168</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A1:R1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="whole" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรอกค่าร้อยละ 0–100" promptTitle="บันทึกผลจริง" prompt="ผลจริงสะสม (%) 0–100" sqref="E5:P8" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>0</formula1>
       <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R5:AC8" xr:uid="{ECE862FD-7CF0-5949-B4C9-2FE03C547C02}">
+      <formula1>"ยังไม่ดำเนินการ,อยู่ระหว่างดำเนินการ,ดำเนินการเสร็จสิ้น"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13593,7 +11336,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -13602,11 +11345,12 @@
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="16" width="6.5" customWidth="1"/>
     <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="18" max="29" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>55</v>
+    <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>67</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -13626,9 +11370,9 @@
       <c r="Q1" s="13"/>
       <c r="R1" s="13"/>
     </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>56</v>
+    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -13648,89 +11392,125 @@
       <c r="Q2" s="13"/>
       <c r="R2" s="13"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="L4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="M4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="Q4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="R4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="S4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="T4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="U4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="V4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="W4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="X4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="Y4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="AA4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
+    <row r="5" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="17"/>
     </row>
-    <row r="6" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D6" s="10">
         <v>1</v>
@@ -13754,16 +11534,52 @@
       <c r="O6" s="11"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="8"/>
+      <c r="R6" t="s">
+        <v>168</v>
+      </c>
+      <c r="S6" t="s">
+        <v>168</v>
+      </c>
+      <c r="T6" t="s">
+        <v>168</v>
+      </c>
+      <c r="U6" t="s">
+        <v>168</v>
+      </c>
+      <c r="V6" t="s">
+        <v>168</v>
+      </c>
+      <c r="W6" t="s">
+        <v>168</v>
+      </c>
+      <c r="X6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D7" s="10">
         <v>2</v>
@@ -13793,16 +11609,52 @@
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="8"/>
+      <c r="R7" t="s">
+        <v>168</v>
+      </c>
+      <c r="S7" t="s">
+        <v>168</v>
+      </c>
+      <c r="T7" t="s">
+        <v>168</v>
+      </c>
+      <c r="U7" t="s">
+        <v>168</v>
+      </c>
+      <c r="V7" t="s">
+        <v>168</v>
+      </c>
+      <c r="W7" t="s">
+        <v>168</v>
+      </c>
+      <c r="X7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D8" s="10">
         <v>2</v>
@@ -13832,37 +11684,73 @@
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="8"/>
+      <c r="R8" t="s">
+        <v>168</v>
+      </c>
+      <c r="S8" t="s">
+        <v>168</v>
+      </c>
+      <c r="T8" t="s">
+        <v>168</v>
+      </c>
+      <c r="U8" t="s">
+        <v>168</v>
+      </c>
+      <c r="V8" t="s">
+        <v>168</v>
+      </c>
+      <c r="W8" t="s">
+        <v>168</v>
+      </c>
+      <c r="X8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="9" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
+    <row r="9" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="17"/>
     </row>
-    <row r="10" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D10" s="10">
         <v>2</v>
@@ -13886,16 +11774,52 @@
       <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="8"/>
+      <c r="R10" t="s">
+        <v>168</v>
+      </c>
+      <c r="S10" t="s">
+        <v>168</v>
+      </c>
+      <c r="T10" t="s">
+        <v>168</v>
+      </c>
+      <c r="U10" t="s">
+        <v>168</v>
+      </c>
+      <c r="V10" t="s">
+        <v>168</v>
+      </c>
+      <c r="W10" t="s">
+        <v>168</v>
+      </c>
+      <c r="X10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="11" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D11" s="10">
         <v>3</v>
@@ -13925,16 +11849,52 @@
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
       <c r="Q11" s="8"/>
+      <c r="R11" t="s">
+        <v>168</v>
+      </c>
+      <c r="S11" t="s">
+        <v>168</v>
+      </c>
+      <c r="T11" t="s">
+        <v>168</v>
+      </c>
+      <c r="U11" t="s">
+        <v>168</v>
+      </c>
+      <c r="V11" t="s">
+        <v>168</v>
+      </c>
+      <c r="W11" t="s">
+        <v>168</v>
+      </c>
+      <c r="X11" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="12" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D12" s="10">
         <v>5</v>
@@ -13964,37 +11924,73 @@
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="8"/>
+      <c r="R12" t="s">
+        <v>168</v>
+      </c>
+      <c r="S12" t="s">
+        <v>168</v>
+      </c>
+      <c r="T12" t="s">
+        <v>168</v>
+      </c>
+      <c r="U12" t="s">
+        <v>168</v>
+      </c>
+      <c r="V12" t="s">
+        <v>168</v>
+      </c>
+      <c r="W12" t="s">
+        <v>168</v>
+      </c>
+      <c r="X12" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="13" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
+    <row r="13" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="17"/>
     </row>
-    <row r="14" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D14" s="10">
         <v>2</v>
@@ -14024,16 +12020,52 @@
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="8"/>
+      <c r="R14" t="s">
+        <v>168</v>
+      </c>
+      <c r="S14" t="s">
+        <v>168</v>
+      </c>
+      <c r="T14" t="s">
+        <v>168</v>
+      </c>
+      <c r="U14" t="s">
+        <v>168</v>
+      </c>
+      <c r="V14" t="s">
+        <v>168</v>
+      </c>
+      <c r="W14" t="s">
+        <v>168</v>
+      </c>
+      <c r="X14" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="15" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D15" s="10">
         <v>4</v>
@@ -14063,16 +12095,52 @@
       <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="8"/>
+      <c r="R15" t="s">
+        <v>168</v>
+      </c>
+      <c r="S15" t="s">
+        <v>168</v>
+      </c>
+      <c r="T15" t="s">
+        <v>168</v>
+      </c>
+      <c r="U15" t="s">
+        <v>168</v>
+      </c>
+      <c r="V15" t="s">
+        <v>168</v>
+      </c>
+      <c r="W15" t="s">
+        <v>168</v>
+      </c>
+      <c r="X15" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="16" spans="1:18" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D16" s="10">
         <v>2</v>
@@ -14102,16 +12170,52 @@
       <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="8"/>
+      <c r="R16" t="s">
+        <v>168</v>
+      </c>
+      <c r="S16" t="s">
+        <v>168</v>
+      </c>
+      <c r="T16" t="s">
+        <v>168</v>
+      </c>
+      <c r="U16" t="s">
+        <v>168</v>
+      </c>
+      <c r="V16" t="s">
+        <v>168</v>
+      </c>
+      <c r="W16" t="s">
+        <v>168</v>
+      </c>
+      <c r="X16" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="17" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D17" s="10">
         <v>6</v>
@@ -14141,16 +12245,52 @@
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="8"/>
+      <c r="R17" t="s">
+        <v>168</v>
+      </c>
+      <c r="S17" t="s">
+        <v>168</v>
+      </c>
+      <c r="T17" t="s">
+        <v>168</v>
+      </c>
+      <c r="U17" t="s">
+        <v>168</v>
+      </c>
+      <c r="V17" t="s">
+        <v>168</v>
+      </c>
+      <c r="W17" t="s">
+        <v>168</v>
+      </c>
+      <c r="X17" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="18" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D18" s="10">
         <v>3</v>
@@ -14180,37 +12320,73 @@
       <c r="O18" s="11"/>
       <c r="P18" s="11"/>
       <c r="Q18" s="8"/>
+      <c r="R18" t="s">
+        <v>168</v>
+      </c>
+      <c r="S18" t="s">
+        <v>168</v>
+      </c>
+      <c r="T18" t="s">
+        <v>168</v>
+      </c>
+      <c r="U18" t="s">
+        <v>168</v>
+      </c>
+      <c r="V18" t="s">
+        <v>168</v>
+      </c>
+      <c r="W18" t="s">
+        <v>168</v>
+      </c>
+      <c r="X18" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="19" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
+    <row r="19" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="17"/>
     </row>
-    <row r="20" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D20" s="10">
         <v>4</v>
@@ -14234,16 +12410,52 @@
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
       <c r="Q20" s="8"/>
+      <c r="R20" t="s">
+        <v>168</v>
+      </c>
+      <c r="S20" t="s">
+        <v>168</v>
+      </c>
+      <c r="T20" t="s">
+        <v>168</v>
+      </c>
+      <c r="U20" t="s">
+        <v>168</v>
+      </c>
+      <c r="V20" t="s">
+        <v>168</v>
+      </c>
+      <c r="W20" t="s">
+        <v>168</v>
+      </c>
+      <c r="X20" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="21" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D21" s="10">
         <v>4</v>
@@ -14273,16 +12485,52 @@
       <c r="O21" s="11"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="8"/>
+      <c r="R21" t="s">
+        <v>168</v>
+      </c>
+      <c r="S21" t="s">
+        <v>168</v>
+      </c>
+      <c r="T21" t="s">
+        <v>168</v>
+      </c>
+      <c r="U21" t="s">
+        <v>168</v>
+      </c>
+      <c r="V21" t="s">
+        <v>168</v>
+      </c>
+      <c r="W21" t="s">
+        <v>168</v>
+      </c>
+      <c r="X21" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="22" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D22" s="10">
         <v>2</v>
@@ -14306,16 +12554,52 @@
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="8"/>
+      <c r="R22" t="s">
+        <v>168</v>
+      </c>
+      <c r="S22" t="s">
+        <v>168</v>
+      </c>
+      <c r="T22" t="s">
+        <v>168</v>
+      </c>
+      <c r="U22" t="s">
+        <v>168</v>
+      </c>
+      <c r="V22" t="s">
+        <v>168</v>
+      </c>
+      <c r="W22" t="s">
+        <v>168</v>
+      </c>
+      <c r="X22" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="23" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D23" s="10">
         <v>2</v>
@@ -14345,16 +12629,52 @@
       <c r="O23" s="11"/>
       <c r="P23" s="11"/>
       <c r="Q23" s="8"/>
+      <c r="R23" t="s">
+        <v>168</v>
+      </c>
+      <c r="S23" t="s">
+        <v>168</v>
+      </c>
+      <c r="T23" t="s">
+        <v>168</v>
+      </c>
+      <c r="U23" t="s">
+        <v>168</v>
+      </c>
+      <c r="V23" t="s">
+        <v>168</v>
+      </c>
+      <c r="W23" t="s">
+        <v>168</v>
+      </c>
+      <c r="X23" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="24" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D24" s="10">
         <v>2</v>
@@ -14384,16 +12704,52 @@
       <c r="O24" s="11"/>
       <c r="P24" s="11"/>
       <c r="Q24" s="8"/>
+      <c r="R24" t="s">
+        <v>168</v>
+      </c>
+      <c r="S24" t="s">
+        <v>168</v>
+      </c>
+      <c r="T24" t="s">
+        <v>168</v>
+      </c>
+      <c r="U24" t="s">
+        <v>168</v>
+      </c>
+      <c r="V24" t="s">
+        <v>168</v>
+      </c>
+      <c r="W24" t="s">
+        <v>168</v>
+      </c>
+      <c r="X24" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="25" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D25" s="10">
         <v>2</v>
@@ -14423,16 +12779,52 @@
       <c r="O25" s="11"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="8"/>
+      <c r="R25" t="s">
+        <v>168</v>
+      </c>
+      <c r="S25" t="s">
+        <v>168</v>
+      </c>
+      <c r="T25" t="s">
+        <v>168</v>
+      </c>
+      <c r="U25" t="s">
+        <v>168</v>
+      </c>
+      <c r="V25" t="s">
+        <v>168</v>
+      </c>
+      <c r="W25" t="s">
+        <v>168</v>
+      </c>
+      <c r="X25" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="26" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D26" s="10">
         <v>4</v>
@@ -14462,37 +12854,73 @@
       <c r="O26" s="11"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="8"/>
+      <c r="R26" t="s">
+        <v>168</v>
+      </c>
+      <c r="S26" t="s">
+        <v>168</v>
+      </c>
+      <c r="T26" t="s">
+        <v>168</v>
+      </c>
+      <c r="U26" t="s">
+        <v>168</v>
+      </c>
+      <c r="V26" t="s">
+        <v>168</v>
+      </c>
+      <c r="W26" t="s">
+        <v>168</v>
+      </c>
+      <c r="X26" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="27" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
+    <row r="27" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="17"/>
     </row>
-    <row r="28" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="D28" s="10">
         <v>2</v>
@@ -14516,16 +12944,52 @@
       <c r="O28" s="11"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="8"/>
+      <c r="R28" t="s">
+        <v>168</v>
+      </c>
+      <c r="S28" t="s">
+        <v>168</v>
+      </c>
+      <c r="T28" t="s">
+        <v>168</v>
+      </c>
+      <c r="U28" t="s">
+        <v>168</v>
+      </c>
+      <c r="V28" t="s">
+        <v>168</v>
+      </c>
+      <c r="W28" t="s">
+        <v>168</v>
+      </c>
+      <c r="X28" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="29" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D29" s="10">
         <v>2</v>
@@ -14551,16 +13015,52 @@
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
       <c r="Q29" s="8"/>
+      <c r="R29" t="s">
+        <v>168</v>
+      </c>
+      <c r="S29" t="s">
+        <v>168</v>
+      </c>
+      <c r="T29" t="s">
+        <v>168</v>
+      </c>
+      <c r="U29" t="s">
+        <v>168</v>
+      </c>
+      <c r="V29" t="s">
+        <v>168</v>
+      </c>
+      <c r="W29" t="s">
+        <v>168</v>
+      </c>
+      <c r="X29" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="30" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D30" s="10">
         <v>3</v>
@@ -14590,16 +13090,52 @@
       <c r="O30" s="11"/>
       <c r="P30" s="11"/>
       <c r="Q30" s="8"/>
+      <c r="R30" t="s">
+        <v>168</v>
+      </c>
+      <c r="S30" t="s">
+        <v>168</v>
+      </c>
+      <c r="T30" t="s">
+        <v>168</v>
+      </c>
+      <c r="U30" t="s">
+        <v>168</v>
+      </c>
+      <c r="V30" t="s">
+        <v>168</v>
+      </c>
+      <c r="W30" t="s">
+        <v>168</v>
+      </c>
+      <c r="X30" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="31" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D31" s="10">
         <v>1</v>
@@ -14623,16 +13159,52 @@
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="8"/>
+      <c r="R31" t="s">
+        <v>168</v>
+      </c>
+      <c r="S31" t="s">
+        <v>168</v>
+      </c>
+      <c r="T31" t="s">
+        <v>168</v>
+      </c>
+      <c r="U31" t="s">
+        <v>168</v>
+      </c>
+      <c r="V31" t="s">
+        <v>168</v>
+      </c>
+      <c r="W31" t="s">
+        <v>168</v>
+      </c>
+      <c r="X31" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="32" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D32" s="10">
         <v>1</v>
@@ -14662,16 +13234,52 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
       <c r="Q32" s="8"/>
+      <c r="R32" t="s">
+        <v>168</v>
+      </c>
+      <c r="S32" t="s">
+        <v>168</v>
+      </c>
+      <c r="T32" t="s">
+        <v>168</v>
+      </c>
+      <c r="U32" t="s">
+        <v>168</v>
+      </c>
+      <c r="V32" t="s">
+        <v>168</v>
+      </c>
+      <c r="W32" t="s">
+        <v>168</v>
+      </c>
+      <c r="X32" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="33" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D33" s="10">
         <v>1</v>
@@ -14701,16 +13309,52 @@
       <c r="O33" s="11"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="8"/>
+      <c r="R33" t="s">
+        <v>168</v>
+      </c>
+      <c r="S33" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" t="s">
+        <v>168</v>
+      </c>
+      <c r="U33" t="s">
+        <v>168</v>
+      </c>
+      <c r="V33" t="s">
+        <v>168</v>
+      </c>
+      <c r="W33" t="s">
+        <v>168</v>
+      </c>
+      <c r="X33" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="34" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="D34" s="10">
         <v>2</v>
@@ -14740,37 +13384,73 @@
       <c r="O34" s="11"/>
       <c r="P34" s="11"/>
       <c r="Q34" s="8"/>
+      <c r="R34" t="s">
+        <v>168</v>
+      </c>
+      <c r="S34" t="s">
+        <v>168</v>
+      </c>
+      <c r="T34" t="s">
+        <v>168</v>
+      </c>
+      <c r="U34" t="s">
+        <v>168</v>
+      </c>
+      <c r="V34" t="s">
+        <v>168</v>
+      </c>
+      <c r="W34" t="s">
+        <v>168</v>
+      </c>
+      <c r="X34" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="35" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
+    <row r="35" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="17"/>
     </row>
-    <row r="36" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D36" s="10">
         <v>5</v>
@@ -14800,16 +13480,52 @@
       <c r="O36" s="11"/>
       <c r="P36" s="11"/>
       <c r="Q36" s="8"/>
+      <c r="R36" t="s">
+        <v>168</v>
+      </c>
+      <c r="S36" t="s">
+        <v>168</v>
+      </c>
+      <c r="T36" t="s">
+        <v>168</v>
+      </c>
+      <c r="U36" t="s">
+        <v>168</v>
+      </c>
+      <c r="V36" t="s">
+        <v>168</v>
+      </c>
+      <c r="W36" t="s">
+        <v>168</v>
+      </c>
+      <c r="X36" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="37" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D37" s="10">
         <v>2</v>
@@ -14839,16 +13555,52 @@
       <c r="O37" s="11"/>
       <c r="P37" s="11"/>
       <c r="Q37" s="8"/>
+      <c r="R37" t="s">
+        <v>168</v>
+      </c>
+      <c r="S37" t="s">
+        <v>168</v>
+      </c>
+      <c r="T37" t="s">
+        <v>168</v>
+      </c>
+      <c r="U37" t="s">
+        <v>168</v>
+      </c>
+      <c r="V37" t="s">
+        <v>168</v>
+      </c>
+      <c r="W37" t="s">
+        <v>168</v>
+      </c>
+      <c r="X37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="38" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D38" s="10">
         <v>3</v>
@@ -14878,37 +13630,73 @@
       <c r="O38" s="11"/>
       <c r="P38" s="11"/>
       <c r="Q38" s="8"/>
+      <c r="R38" t="s">
+        <v>168</v>
+      </c>
+      <c r="S38" t="s">
+        <v>168</v>
+      </c>
+      <c r="T38" t="s">
+        <v>168</v>
+      </c>
+      <c r="U38" t="s">
+        <v>168</v>
+      </c>
+      <c r="V38" t="s">
+        <v>168</v>
+      </c>
+      <c r="W38" t="s">
+        <v>168</v>
+      </c>
+      <c r="X38" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="39" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15"/>
+    <row r="39" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="16"/>
+      <c r="Q39" s="17"/>
     </row>
-    <row r="40" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D40" s="10">
         <v>1</v>
@@ -14938,16 +13726,52 @@
       <c r="O40" s="11"/>
       <c r="P40" s="11"/>
       <c r="Q40" s="8"/>
+      <c r="R40" t="s">
+        <v>168</v>
+      </c>
+      <c r="S40" t="s">
+        <v>168</v>
+      </c>
+      <c r="T40" t="s">
+        <v>168</v>
+      </c>
+      <c r="U40" t="s">
+        <v>168</v>
+      </c>
+      <c r="V40" t="s">
+        <v>168</v>
+      </c>
+      <c r="W40" t="s">
+        <v>168</v>
+      </c>
+      <c r="X40" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="41" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D41" s="10">
         <v>2</v>
@@ -14977,16 +13801,52 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
       <c r="Q41" s="8"/>
+      <c r="R41" t="s">
+        <v>168</v>
+      </c>
+      <c r="S41" t="s">
+        <v>168</v>
+      </c>
+      <c r="T41" t="s">
+        <v>168</v>
+      </c>
+      <c r="U41" t="s">
+        <v>168</v>
+      </c>
+      <c r="V41" t="s">
+        <v>168</v>
+      </c>
+      <c r="W41" t="s">
+        <v>168</v>
+      </c>
+      <c r="X41" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="42" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D42" s="10">
         <v>2</v>
@@ -15016,16 +13876,52 @@
       <c r="O42" s="11"/>
       <c r="P42" s="11"/>
       <c r="Q42" s="8"/>
+      <c r="R42" t="s">
+        <v>168</v>
+      </c>
+      <c r="S42" t="s">
+        <v>168</v>
+      </c>
+      <c r="T42" t="s">
+        <v>168</v>
+      </c>
+      <c r="U42" t="s">
+        <v>168</v>
+      </c>
+      <c r="V42" t="s">
+        <v>168</v>
+      </c>
+      <c r="W42" t="s">
+        <v>168</v>
+      </c>
+      <c r="X42" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="43" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D43" s="10">
         <v>2</v>
@@ -15055,16 +13951,52 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
       <c r="Q43" s="8"/>
+      <c r="R43" t="s">
+        <v>168</v>
+      </c>
+      <c r="S43" t="s">
+        <v>168</v>
+      </c>
+      <c r="T43" t="s">
+        <v>168</v>
+      </c>
+      <c r="U43" t="s">
+        <v>168</v>
+      </c>
+      <c r="V43" t="s">
+        <v>168</v>
+      </c>
+      <c r="W43" t="s">
+        <v>168</v>
+      </c>
+      <c r="X43" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="44" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D44" s="10">
         <v>1</v>
@@ -15094,37 +14026,73 @@
       <c r="O44" s="11"/>
       <c r="P44" s="11"/>
       <c r="Q44" s="8"/>
+      <c r="R44" t="s">
+        <v>168</v>
+      </c>
+      <c r="S44" t="s">
+        <v>168</v>
+      </c>
+      <c r="T44" t="s">
+        <v>168</v>
+      </c>
+      <c r="U44" t="s">
+        <v>168</v>
+      </c>
+      <c r="V44" t="s">
+        <v>168</v>
+      </c>
+      <c r="W44" t="s">
+        <v>168</v>
+      </c>
+      <c r="X44" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="45" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="15"/>
-      <c r="O45" s="15"/>
-      <c r="P45" s="15"/>
-      <c r="Q45" s="15"/>
+    <row r="45" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="17"/>
     </row>
-    <row r="46" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D46" s="10">
         <v>2</v>
@@ -15154,16 +14122,52 @@
       <c r="O46" s="11"/>
       <c r="P46" s="11"/>
       <c r="Q46" s="8"/>
+      <c r="R46" t="s">
+        <v>168</v>
+      </c>
+      <c r="S46" t="s">
+        <v>168</v>
+      </c>
+      <c r="T46" t="s">
+        <v>168</v>
+      </c>
+      <c r="U46" t="s">
+        <v>168</v>
+      </c>
+      <c r="V46" t="s">
+        <v>168</v>
+      </c>
+      <c r="W46" t="s">
+        <v>168</v>
+      </c>
+      <c r="X46" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="47" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D47" s="10">
         <v>2</v>
@@ -15193,16 +14197,52 @@
       <c r="O47" s="11"/>
       <c r="P47" s="11"/>
       <c r="Q47" s="8"/>
+      <c r="R47" t="s">
+        <v>168</v>
+      </c>
+      <c r="S47" t="s">
+        <v>168</v>
+      </c>
+      <c r="T47" t="s">
+        <v>168</v>
+      </c>
+      <c r="U47" t="s">
+        <v>168</v>
+      </c>
+      <c r="V47" t="s">
+        <v>168</v>
+      </c>
+      <c r="W47" t="s">
+        <v>168</v>
+      </c>
+      <c r="X47" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="48" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D48" s="10">
         <v>4</v>
@@ -15232,37 +14272,73 @@
       <c r="O48" s="11"/>
       <c r="P48" s="11"/>
       <c r="Q48" s="8"/>
+      <c r="R48" t="s">
+        <v>168</v>
+      </c>
+      <c r="S48" t="s">
+        <v>168</v>
+      </c>
+      <c r="T48" t="s">
+        <v>168</v>
+      </c>
+      <c r="U48" t="s">
+        <v>168</v>
+      </c>
+      <c r="V48" t="s">
+        <v>168</v>
+      </c>
+      <c r="W48" t="s">
+        <v>168</v>
+      </c>
+      <c r="X48" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="49" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="15"/>
-      <c r="O49" s="15"/>
-      <c r="P49" s="15"/>
-      <c r="Q49" s="15"/>
+    <row r="49" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="17"/>
     </row>
-    <row r="50" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D50" s="10">
         <v>6</v>
@@ -15292,16 +14368,52 @@
       <c r="O50" s="11"/>
       <c r="P50" s="11"/>
       <c r="Q50" s="8"/>
+      <c r="R50" t="s">
+        <v>168</v>
+      </c>
+      <c r="S50" t="s">
+        <v>168</v>
+      </c>
+      <c r="T50" t="s">
+        <v>168</v>
+      </c>
+      <c r="U50" t="s">
+        <v>168</v>
+      </c>
+      <c r="V50" t="s">
+        <v>168</v>
+      </c>
+      <c r="W50" t="s">
+        <v>168</v>
+      </c>
+      <c r="X50" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="51" spans="1:17" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D51" s="10">
         <v>4</v>
@@ -15331,25 +14443,64 @@
       <c r="O51" s="11"/>
       <c r="P51" s="11"/>
       <c r="Q51" s="8"/>
+      <c r="R51" t="s">
+        <v>168</v>
+      </c>
+      <c r="S51" t="s">
+        <v>168</v>
+      </c>
+      <c r="T51" t="s">
+        <v>168</v>
+      </c>
+      <c r="U51" t="s">
+        <v>168</v>
+      </c>
+      <c r="V51" t="s">
+        <v>168</v>
+      </c>
+      <c r="W51" t="s">
+        <v>168</v>
+      </c>
+      <c r="X51" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>168</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A19:Q19"/>
+    <mergeCell ref="A49:Q49"/>
     <mergeCell ref="A45:Q45"/>
-    <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="A49:Q49"/>
     <mergeCell ref="A13:Q13"/>
     <mergeCell ref="A9:Q9"/>
     <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="A5:Q5"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A39:Q39"/>
     <mergeCell ref="A35:Q35"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="whole" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรอกค่าร้อยละ 0–100" promptTitle="บันทึกผลจริง" prompt="ผลจริงสะสม (%) 0–100" sqref="E5:P51" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>0</formula1>
       <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6:AC8 R10:AC12 R14:AC18 R20:AC26 R28:AC34 R36:AC38 R40:AC44 R46:AC48 R50:AC51" xr:uid="{08554CBC-E6BA-5A48-84DD-E0E4FA7C60C8}">
+      <formula1>"ยังไม่ดำเนินการ,อยู่ระหว่างดำเนินการ,ดำเนินการเสร็จสิ้น"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CG_2569_บันทึกผลจริง_template.xlsx
+++ b/CG_2569_บันทึกผลจริง_template.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10306,18 +10306,18 @@
     <xf numFmtId="1" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10692,7 +10692,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13"/>
@@ -10714,7 +10714,7 @@
       <c r="R1" s="13"/>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -11065,7 +11065,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="13"/>
@@ -11087,7 +11087,7 @@
       <c r="R1" s="13"/>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="17" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="13"/>
@@ -11573,7 +11573,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>60</v>
       </c>
       <c r="B1" s="13"/>
@@ -11595,7 +11595,7 @@
       <c r="R1" s="13"/>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="17" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="13"/>
@@ -11967,7 +11967,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="13"/>
@@ -11989,7 +11989,7 @@
       <c r="R1" s="13"/>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="17" t="s">
         <v>68</v>
       </c>
       <c r="B2" s="13"/>
@@ -12100,25 +12100,25 @@
       </c>
     </row>
     <row r="5" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="17"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="16"/>
     </row>
     <row r="6" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
@@ -12277,25 +12277,25 @@
       </c>
     </row>
     <row r="9" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="17"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="16"/>
     </row>
     <row r="10" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
@@ -12454,25 +12454,25 @@
       </c>
     </row>
     <row r="13" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="17"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="16"/>
     </row>
     <row r="14" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
@@ -12742,25 +12742,25 @@
       <c r="Q18" s="8"/>
     </row>
     <row r="19" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="17"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="16"/>
     </row>
     <row r="20" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
@@ -13132,25 +13132,25 @@
       </c>
     </row>
     <row r="27" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="17"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="16"/>
     </row>
     <row r="28" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
@@ -13512,25 +13512,25 @@
       </c>
     </row>
     <row r="35" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="17"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="16"/>
     </row>
     <row r="36" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
@@ -13704,25 +13704,25 @@
       </c>
     </row>
     <row r="39" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="17"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="16"/>
     </row>
     <row r="40" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
@@ -14010,25 +14010,25 @@
       </c>
     </row>
     <row r="45" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
-      <c r="O45" s="16"/>
-      <c r="P45" s="16"/>
-      <c r="Q45" s="17"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+      <c r="Q45" s="16"/>
     </row>
     <row r="46" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
@@ -14202,25 +14202,25 @@
       </c>
     </row>
     <row r="49" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
-      <c r="O49" s="16"/>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="17"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="16"/>
     </row>
     <row r="50" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">

--- a/CG_2569_บันทึกผลจริง_template.xlsx
+++ b/CG_2569_บันทึกผลจริง_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devill/1_กฟน./2569/Dashborad_CG/DB_CG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D357CF-0F08-0241-B21F-0E0A1FF5C67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9B3328-3B92-3E47-A43C-B59F90F2F0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14720" yWindow="660" windowWidth="14680" windowHeight="16980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="คำแนะนำ" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,20 @@
     <sheet name="Fraud" sheetId="4" r:id="rId4"/>
     <sheet name="9 หมวด" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2702,6 +2715,306 @@
         <r>
           <rPr>
             <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>ธ</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>ค</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>.: 100.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 10.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>ก</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>พ</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>.: 20.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 30.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000010000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 40.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000011000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 50.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 60.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ค.: 70.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>ส</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>ค</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>.: 80.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ย.: 85.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000016000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ต.ค.: 90.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000017000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ย.: 95.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000018000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
             <family val="2"/>
@@ -2711,21 +3024,301 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ม.ค.: 10.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000019000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 10.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ค.: 20.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000020000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ส.ค.: 30.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000021000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ย.: 40.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000022000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ต.ค.: 60.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000023000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ย.: 80.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000024000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ธ.ค.: 100.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000025000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ม.ค.: 30.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000026000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.พ.: 60.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000027000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มี.ค.: 100.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000028000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน เม.ย.: 100.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000029000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน พ.ค.: 100.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน มิ.ย.: 100.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ค.: 100.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ส.ค.: 100.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>เป้าหมายสะสมเดือน ก.ย.: 100.0%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002E000000}">
       <text>
         <r>
           <rPr>
@@ -2752,7 +3345,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>ก</t>
+          <t>ต</t>
         </r>
         <r>
           <rPr>
@@ -2770,7 +3363,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>พ</t>
+          <t>ค</t>
         </r>
         <r>
           <rPr>
@@ -2779,499 +3372,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>.: 20.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน มี.ค.: 30.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน เม.ย.: 40.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน พ.ค.: 50.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน มิ.ย.: 60.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000013000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ก.ค.: 70.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000014000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ส</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>ค</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>.: 80.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000015000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ก.ย.: 85.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000016000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ต.ค.: 90.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000017000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน พ.ย.: 95.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ธ.ค.: 100.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ม.ค.: 0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ก.พ.: 0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน มี.ค.: 0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน เม.ย.: 0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน พ.ค.: 0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน มิ.ย.: 10.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00001F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ก.ค.: 20.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000020000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ส.ค.: 30.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000021000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ก.ย.: 40.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000022000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ต.ค.: 60.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000023000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน พ.ย.: 80.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000024000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ธ.ค.: 100.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000025000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ม.ค.: 30.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000026000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ก.พ.: 60.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000027000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน มี.ค.: 100.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000028000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน เม.ย.: 100.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000029000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน พ.ค.: 100.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน มิ.ย.: 100.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ก.ค.: 100.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ส.ค.: 100.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ก.ย.: 100.0%</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00002E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>เป้าหมายสะสมเดือน ต.ค.: 100.0%</t>
+          <t>.: 100.0%</t>
         </r>
       </text>
     </comment>
@@ -9592,7 +9693,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="181">
   <si>
     <t>แผนองค์กรโปร่งใสมีคุณธรรมตามแนวทาง ITA (Integrity and Transparency Assessment) ประจำปี 2569</t>
   </si>
@@ -10102,6 +10203,39 @@
   </si>
   <si>
     <t>ดำเนินการเสร็จสิ้น</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ ม.ค.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ ก.พ.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ มี.ค.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ เม.ย.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ พ.ค.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ มิ.ย.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ ก.ค.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ ส.ค.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ ก.ย.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ พ.ย.</t>
+  </si>
+  <si>
+    <t>สรุปผลการดำเนินการ ธ.ค.</t>
   </si>
 </sst>
 </file>
@@ -10182,7 +10316,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10219,8 +10353,14 @@
         <fgColor rgb="FFE6F2EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -10267,11 +10407,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC8D4CE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC8D4CE"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -10306,18 +10457,25 @@
     <xf numFmtId="1" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10679,7 +10837,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AP8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -10691,51 +10849,51 @@
     <col min="18" max="29" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:42" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
     </row>
-    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
     </row>
-    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" ht="52" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -10823,8 +10981,47 @@
       <c r="AC4" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="AD4" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE4" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF4" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG4" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="AH4" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AI4" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK4" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AM4" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN4" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO4" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="AP4" s="12" t="s">
+        <v>180</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
@@ -10865,8 +11062,14 @@
       <c r="T5" t="s">
         <v>169</v>
       </c>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="14"/>
     </row>
-    <row r="6" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>34</v>
       </c>
@@ -10922,8 +11125,14 @@
       <c r="W6" t="s">
         <v>167</v>
       </c>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
     </row>
-    <row r="7" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
@@ -10977,8 +11186,14 @@
       <c r="W7" t="s">
         <v>169</v>
       </c>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="14"/>
     </row>
-    <row r="8" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>39</v>
       </c>
@@ -11030,6 +11245,12 @@
       <c r="W8" t="s">
         <v>168</v>
       </c>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11052,7 +11273,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AP10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -11064,51 +11285,51 @@
     <col min="18" max="29" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:42" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
     </row>
-    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
     </row>
-    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -11196,8 +11417,47 @@
       <c r="AC4" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="AD4" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE4" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF4" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG4" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="AH4" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AI4" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK4" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AM4" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN4" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO4" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="AP4" s="12" t="s">
+        <v>180</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
@@ -11253,8 +11513,14 @@
       <c r="W5" t="s">
         <v>167</v>
       </c>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="14"/>
     </row>
-    <row r="6" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>34</v>
       </c>
@@ -11310,8 +11576,14 @@
       <c r="W6" t="s">
         <v>167</v>
       </c>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
     </row>
-    <row r="7" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
@@ -11367,8 +11639,14 @@
       <c r="W7" t="s">
         <v>167</v>
       </c>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="14"/>
     </row>
-    <row r="8" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>39</v>
       </c>
@@ -11424,8 +11702,14 @@
       <c r="W8" t="s">
         <v>168</v>
       </c>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
     </row>
-    <row r="9" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>56</v>
       </c>
@@ -11481,8 +11765,14 @@
       <c r="W9" t="s">
         <v>167</v>
       </c>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
     </row>
-    <row r="10" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>58</v>
       </c>
@@ -11538,6 +11828,12 @@
       <c r="W10" t="s">
         <v>167</v>
       </c>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="14"/>
+      <c r="AF10" s="14"/>
+      <c r="AG10" s="14"/>
+      <c r="AH10" s="14"/>
+      <c r="AI10" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11560,7 +11856,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AP8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -11572,51 +11868,51 @@
     <col min="18" max="29" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:42" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
     </row>
-    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
     </row>
-    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -11704,8 +12000,47 @@
       <c r="AC4" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="AD4" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE4" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF4" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG4" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="AH4" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AI4" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK4" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AM4" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN4" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO4" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="AP4" s="12" t="s">
+        <v>180</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>31</v>
       </c>
@@ -11761,8 +12096,14 @@
       <c r="W5" t="s">
         <v>167</v>
       </c>
+      <c r="AD5" s="14"/>
+      <c r="AE5" s="14"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="14"/>
     </row>
-    <row r="6" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>34</v>
       </c>
@@ -11818,8 +12159,14 @@
       <c r="W6" t="s">
         <v>167</v>
       </c>
+      <c r="AD6" s="14"/>
+      <c r="AE6" s="14"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
     </row>
-    <row r="7" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
@@ -11875,8 +12222,14 @@
       <c r="W7" t="s">
         <v>167</v>
       </c>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="14"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="14"/>
     </row>
-    <row r="8" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>39</v>
       </c>
@@ -11932,6 +12285,12 @@
       <c r="W8" t="s">
         <v>167</v>
       </c>
+      <c r="AD8" s="14"/>
+      <c r="AE8" s="14"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="14"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11954,7 +12313,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AP51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -11966,51 +12325,51 @@
     <col min="18" max="29" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:42" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
     </row>
-    <row r="2" spans="1:29" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
     </row>
-    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -12098,29 +12457,68 @@
       <c r="AC4" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="AD4" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="AE4" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF4" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG4" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="AH4" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="AI4" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK4" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="AL4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="AM4" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="AN4" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="AO4" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="AP4" s="12" t="s">
+        <v>180</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="16"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="20"/>
     </row>
-    <row r="6" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
@@ -12162,7 +12560,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>73</v>
       </c>
@@ -12219,7 +12617,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>75</v>
       </c>
@@ -12276,28 +12674,34 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="16"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="20"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="14"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="14"/>
     </row>
-    <row r="10" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>79</v>
       </c>
@@ -12339,7 +12743,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>82</v>
       </c>
@@ -12396,7 +12800,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>85</v>
       </c>
@@ -12453,28 +12857,34 @@
         <v>167</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="16"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="20"/>
+      <c r="AD13" s="14"/>
+      <c r="AE13" s="14"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="14"/>
     </row>
-    <row r="14" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>88</v>
       </c>
@@ -12531,7 +12941,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>91</v>
       </c>
@@ -12588,7 +12998,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>93</v>
       </c>
@@ -12645,7 +13055,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>95</v>
       </c>
@@ -12702,7 +13112,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>97</v>
       </c>
@@ -12741,28 +13151,34 @@
       <c r="P18" s="11"/>
       <c r="Q18" s="8"/>
     </row>
-    <row r="19" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="16"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="20"/>
+      <c r="AD19" s="14"/>
+      <c r="AE19" s="14"/>
+      <c r="AF19" s="14"/>
+      <c r="AG19" s="14"/>
+      <c r="AH19" s="14"/>
+      <c r="AI19" s="14"/>
     </row>
-    <row r="20" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>100</v>
       </c>
@@ -12804,7 +13220,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>103</v>
       </c>
@@ -12861,7 +13277,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>105</v>
       </c>
@@ -12903,7 +13319,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>108</v>
       </c>
@@ -12960,7 +13376,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>110</v>
       </c>
@@ -13017,7 +13433,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>112</v>
       </c>
@@ -13074,7 +13490,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>114</v>
       </c>
@@ -13131,28 +13547,34 @@
         <v>167</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="16"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="20"/>
+      <c r="AD27" s="14"/>
+      <c r="AE27" s="14"/>
+      <c r="AF27" s="14"/>
+      <c r="AG27" s="14"/>
+      <c r="AH27" s="14"/>
+      <c r="AI27" s="14"/>
     </row>
-    <row r="28" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>118</v>
       </c>
@@ -13194,7 +13616,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>120</v>
       </c>
@@ -13241,7 +13663,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>122</v>
       </c>
@@ -13298,7 +13720,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
         <v>124</v>
       </c>
@@ -13340,7 +13762,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>127</v>
       </c>
@@ -13397,7 +13819,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
         <v>129</v>
       </c>
@@ -13454,7 +13876,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>131</v>
       </c>
@@ -13511,28 +13933,34 @@
         <v>167</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="16"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="20"/>
+      <c r="AD35" s="14"/>
+      <c r="AE35" s="14"/>
+      <c r="AF35" s="14"/>
+      <c r="AG35" s="14"/>
+      <c r="AH35" s="14"/>
+      <c r="AI35" s="14"/>
     </row>
-    <row r="36" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="s">
         <v>135</v>
       </c>
@@ -13589,7 +14017,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>138</v>
       </c>
@@ -13646,7 +14074,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="7" t="s">
         <v>141</v>
       </c>
@@ -13703,28 +14131,34 @@
         <v>167</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
+    <row r="39" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="16"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="20"/>
+      <c r="AD39" s="14"/>
+      <c r="AE39" s="14"/>
+      <c r="AF39" s="14"/>
+      <c r="AG39" s="14"/>
+      <c r="AH39" s="14"/>
+      <c r="AI39" s="14"/>
     </row>
-    <row r="40" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
         <v>145</v>
       </c>
@@ -13781,7 +14215,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
         <v>147</v>
       </c>
@@ -13838,7 +14272,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
         <v>149</v>
       </c>
@@ -13895,7 +14329,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="s">
         <v>151</v>
       </c>
@@ -13952,7 +14386,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7" t="s">
         <v>153</v>
       </c>
@@ -14009,28 +14443,34 @@
         <v>167</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="14" t="s">
+    <row r="45" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="15"/>
-      <c r="O45" s="15"/>
-      <c r="P45" s="15"/>
-      <c r="Q45" s="16"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="20"/>
+      <c r="AD45" s="14"/>
+      <c r="AE45" s="14"/>
+      <c r="AF45" s="14"/>
+      <c r="AG45" s="14"/>
+      <c r="AH45" s="14"/>
+      <c r="AI45" s="14"/>
     </row>
-    <row r="46" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7" t="s">
         <v>156</v>
       </c>
@@ -14087,7 +14527,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7" t="s">
         <v>158</v>
       </c>
@@ -14144,7 +14584,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="7" t="s">
         <v>160</v>
       </c>
@@ -14201,28 +14641,34 @@
         <v>167</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="14" t="s">
+    <row r="49" spans="1:35" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="15"/>
-      <c r="O49" s="15"/>
-      <c r="P49" s="15"/>
-      <c r="Q49" s="16"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="19"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="20"/>
+      <c r="AD49" s="14"/>
+      <c r="AE49" s="14"/>
+      <c r="AF49" s="14"/>
+      <c r="AG49" s="14"/>
+      <c r="AH49" s="14"/>
+      <c r="AI49" s="14"/>
     </row>
-    <row r="50" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
         <v>163</v>
       </c>
@@ -14279,7 +14725,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:35" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
         <v>165</v>
       </c>
